--- a/Courses/Term 3/QAM-III/101 DATA - NLP START Concept Sine Jan 5, 2026.xlsx
+++ b/Courses/Term 3/QAM-III/101 DATA - NLP START Concept Sine Jan 5, 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/Data to students - Email/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6AE460-1E6F-924F-8CBB-99ACE6795553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DFFE39-5D23-44CE-AC0F-FC6E85A66E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7820" yWindow="980" windowWidth="25600" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(x-1)(x-2)" sheetId="12" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
@@ -72,6 +73,7 @@
     <definedName name="solver_num" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'(x-1)(x-2)'!$G$8</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'(x-1)(x-2)(x-3)'!$G$8</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'(x-1)(x-2)(x-3)(x-4)(x-5)'!$G$8</definedName>
@@ -122,7 +124,7 @@
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">2</definedName>
@@ -136,7 +138,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -147,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="27">
   <si>
     <t>OFV</t>
   </si>
@@ -226,13 +227,16 @@
   <si>
     <t>VERY VERY HIGH INFINITY</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
@@ -317,9 +321,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -336,6 +340,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -357,7 +362,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -578,6 +583,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -585,7 +591,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5493,55 +5498,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C46F7F7-BBA2-DA4F-917F-106BA51030AA}">
   <dimension ref="A2:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>0</v>
+        <v>268435461</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E8">
         <f>$B$8-1</f>
-        <v>-1</v>
-      </c>
-      <c r="G8" s="8">
-        <f>E8*E9</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+        <v>268435460</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E9">
         <f>$B$8-2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+        <v>268435459</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
@@ -5550,37 +5554,37 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
       <c r="H14" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D15" s="1"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D16" s="1"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>15</v>
       </c>
@@ -5592,7 +5596,7 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0</v>
       </c>
@@ -5606,7 +5610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -5617,7 +5621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5628,7 +5632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -5639,7 +5643,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H24" s="1" t="s">
         <v>23</v>
       </c>
@@ -5653,31 +5657,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2830EB05-6E8C-EE4C-93D1-86A7E2CFA7DB}">
   <dimension ref="A2:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
-    <col min="7" max="7" width="32.5" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>1.4226497303803167</v>
       </c>
@@ -5693,7 +5697,7 @@
         <v>0.38490017945975052</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>-0.57735026961968328</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
@@ -5715,45 +5719,45 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
       <c r="H14" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D15" s="1"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D16" s="1"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H19" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>15</v>
       </c>
@@ -5764,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0</v>
       </c>
@@ -5775,7 +5779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -5786,7 +5790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2</v>
       </c>
@@ -5797,7 +5801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5811,7 +5815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4</v>
       </c>
@@ -5822,7 +5826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J26" s="7">
         <v>1.42</v>
       </c>
@@ -5837,12 +5841,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21E0216-250D-DF47-8C40-284622E3F925}">
   <dimension ref="A2:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5853,17 +5857,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>268435461</v>
       </c>
@@ -5879,7 +5883,7 @@
         <v>1.3937966268311335E+42</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -5888,7 +5892,7 @@
         <v>268435459</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
@@ -5900,7 +5904,7 @@
         <v>268435458</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
@@ -5912,7 +5916,7 @@
         <v>268435457</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
@@ -5921,25 +5925,25 @@
         <v>268435456</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D16" s="1"/>
       <c r="H16" s="10">
         <v>3.63</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
@@ -5950,7 +5954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -5964,7 +5968,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1.5</v>
       </c>
@@ -5975,7 +5979,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5986,7 +5990,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -5997,7 +6001,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4</v>
       </c>
@@ -6014,7 +6018,7 @@
         <v>3.5430000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5</v>
       </c>
@@ -6034,24 +6038,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2145A1B-EBAC-FF4F-A73F-4190B3E32B71}">
   <dimension ref="A2:G24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>8.6388593490949646</v>
       </c>
@@ -6067,7 +6071,7 @@
         <v>6555.8993779696357</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -6076,7 +6080,7 @@
         <v>6.6388593490949646</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6085,7 +6089,7 @@
         <v>5.6388593490949646</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
@@ -6094,7 +6098,7 @@
         <v>4.6388593490949646</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
@@ -6103,7 +6107,7 @@
         <v>3.6388593490949646</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
@@ -6112,7 +6116,7 @@
         <v>2.6388593490949646</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
@@ -6121,7 +6125,7 @@
         <v>1.6388593490949646</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
@@ -6130,7 +6134,7 @@
         <v>0.63885934909496456</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="s">
         <v>12</v>
       </c>
@@ -6139,7 +6143,7 @@
         <v>-0.36114065090503544</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -6148,7 +6152,7 @@
         <v>-1.3611406509050354</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -6159,7 +6163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
@@ -6170,7 +6174,7 @@
         <v>6555</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5</v>
       </c>
@@ -6181,7 +6185,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -6192,7 +6196,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
